--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-09-2025.xlsx
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
